--- a/web/public/forms/gy-unban.xlsx
+++ b/web/public/forms/gy-unban.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="운반계약서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'운반계약서'!$A$1:$X$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'운반계약서'!$A$1:$X$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,29 +36,56 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -65,12 +97,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +116,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,35 +141,53 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X56"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -533,15 +583,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -565,7 +615,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -595,7 +645,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -625,7 +675,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -655,7 +705,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -685,7 +735,7 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
@@ -715,7 +765,7 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
@@ -745,7 +795,7 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
@@ -775,7 +825,7 @@
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
@@ -805,7 +855,7 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
@@ -835,7 +885,7 @@
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n"/>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
@@ -855,7 +905,7 @@
       <c r="X14" s="5" t="n"/>
     </row>
     <row r="15" ht="6" customHeight="1"/>
-    <row r="16" ht="26" customHeight="1">
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>위탁자(이하 「갑」)와 운반자(이하 「을」)는 위 운반에 관하여 다음과 같이 계약을 체결한다.</t>
@@ -864,14 +914,14 @@
     </row>
     <row r="17" ht="6" customHeight="1"/>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>제1조 (목적)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="43.5" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>을은 갑이 지정한 품목을 상차 장소에서 하차 장소까지 운반하고, 갑은 그 대가를 지급한다.</t>
         </is>
@@ -879,14 +929,14 @@
     </row>
     <row r="20" ht="4" customHeight="1"/>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>제2조 (운반 단가)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="43.5" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>운반 대가는 위 단가 기준에 따라 산정한다. 기준이 바뀌는 경우 서면으로 합의한다.</t>
         </is>
@@ -894,14 +944,14 @@
     </row>
     <row r="23" ht="4" customHeight="1"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>제3조 (적재량 준수)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="43.5" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>을은 관계 법령에서 정한 적재량과 운행 기준을 지킨다. 과적으로 발생한 책임은 을이 진다.</t>
         </is>
@@ -909,14 +959,14 @@
     </row>
     <row r="26" ht="4" customHeight="1"/>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>제4조 (대기)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="29" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>갑의 사정으로 상·하차가 지연된 때에는 위 대기료를 지급한다.</t>
         </is>
@@ -924,14 +974,14 @@
     </row>
     <row r="29" ht="4" customHeight="1"/>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>제5조 (운반물의 관리)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="43.5" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>운반 중 운반물의 멸실·훼손에 대한 책임은 을이 진다. 다만 갑의 지시나 불가항력에 의한 경우는 그러하지 아니하다.</t>
         </is>
@@ -939,271 +989,1122 @@
     </row>
     <row r="32" ht="4" customHeight="1"/>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>제6조 (허가와 보험)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="29" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>폐기물 등 허가가 필요한 운반은 을이 유효한 허가와 보험을 갖춘다.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="4" customHeight="1"/>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="1" t="inlineStr">
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="8" customHeight="1"/>
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="8" customHeight="1"/>
+    <row r="40" ht="8" customHeight="1"/>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>제7조 (대금의 지급)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="29" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="43" ht="29" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>갑은 운반 완료를 확인한 후 위 지급기한 안에 대금을 지급한다.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="4" customHeight="1"/>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="1" t="inlineStr">
+    <row r="44" ht="4" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>제8조 (분쟁의 해결)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="43.5" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="46" ht="43.5" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>분쟁은 협의로 해결하되, 협의가 되지 아니한 때에는 관할 법원의 판결에 따른다.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="4" customHeight="1"/>
-    <row r="42" ht="6" customHeight="1"/>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+    <row r="47" ht="4" customHeight="1"/>
+    <row r="48" ht="6" customHeight="1"/>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>상호(성명)</t>
         </is>
       </c>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>사업자등록번호</t>
         </is>
       </c>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="9" t="inlineStr">
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="10" t="inlineStr">
         <is>
           <t>대표자</t>
         </is>
       </c>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="n"/>
-      <c r="O43" s="9" t="inlineStr">
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="n"/>
+      <c r="O49" s="10" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
       </c>
-      <c r="P43" s="5" t="n"/>
-      <c r="Q43" s="5" t="n"/>
-      <c r="R43" s="5" t="n"/>
-      <c r="S43" s="5" t="n"/>
-      <c r="T43" s="5" t="n"/>
-      <c r="U43" s="5" t="n"/>
-      <c r="V43" s="9" t="inlineStr">
+      <c r="P49" s="5" t="n"/>
+      <c r="Q49" s="5" t="n"/>
+      <c r="R49" s="5" t="n"/>
+      <c r="S49" s="5" t="n"/>
+      <c r="T49" s="5" t="n"/>
+      <c r="U49" s="5" t="n"/>
+      <c r="V49" s="10" t="inlineStr">
         <is>
           <t>연락처</t>
         </is>
       </c>
-      <c r="W43" s="5" t="n"/>
-      <c r="X43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="10" t="inlineStr"/>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="10" t="inlineStr"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="10" t="inlineStr"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="n"/>
-      <c r="L44" s="10" t="inlineStr"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="n"/>
-      <c r="O44" s="10" t="inlineStr"/>
-      <c r="P44" s="5" t="n"/>
-      <c r="Q44" s="5" t="n"/>
-      <c r="R44" s="5" t="n"/>
-      <c r="S44" s="5" t="n"/>
-      <c r="T44" s="5" t="n"/>
-      <c r="U44" s="5" t="n"/>
-      <c r="V44" s="10" t="inlineStr"/>
-      <c r="W44" s="5" t="n"/>
-      <c r="X44" s="5" t="n"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="10" t="inlineStr"/>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="10" t="inlineStr"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="10" t="inlineStr"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
-      <c r="L45" s="10" t="inlineStr"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="n"/>
-      <c r="O45" s="10" t="inlineStr"/>
-      <c r="P45" s="5" t="n"/>
-      <c r="Q45" s="5" t="n"/>
-      <c r="R45" s="5" t="n"/>
-      <c r="S45" s="5" t="n"/>
-      <c r="T45" s="5" t="n"/>
-      <c r="U45" s="5" t="n"/>
-      <c r="V45" s="10" t="inlineStr"/>
-      <c r="W45" s="5" t="n"/>
-      <c r="X45" s="5" t="n"/>
-    </row>
-    <row r="46" ht="6" customHeight="1"/>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="W49" s="5" t="n"/>
+      <c r="X49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>갑</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="11" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="11" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="n"/>
+      <c r="O50" s="12" t="n"/>
+      <c r="P50" s="5" t="n"/>
+      <c r="Q50" s="5" t="n"/>
+      <c r="R50" s="5" t="n"/>
+      <c r="S50" s="5" t="n"/>
+      <c r="T50" s="5" t="n"/>
+      <c r="U50" s="5" t="n"/>
+      <c r="V50" s="11" t="n"/>
+      <c r="W50" s="5" t="n"/>
+      <c r="X50" s="5" t="n"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>을</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="11" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="11" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="12" t="n"/>
+      <c r="P51" s="5" t="n"/>
+      <c r="Q51" s="5" t="n"/>
+      <c r="R51" s="5" t="n"/>
+      <c r="S51" s="5" t="n"/>
+      <c r="T51" s="5" t="n"/>
+      <c r="U51" s="5" t="n"/>
+      <c r="V51" s="11" t="n"/>
+      <c r="W51" s="5" t="n"/>
+      <c r="X51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="6" customHeight="1"/>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="6" customHeight="1"/>
-    <row r="49" ht="10" customHeight="1"/>
-    <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="K51" s="12" t="inlineStr">
+    <row r="54" ht="6" customHeight="1"/>
+    <row r="55" ht="10" customHeight="1"/>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="14" t="inlineStr"/>
+      <c r="K57" s="15" t="inlineStr">
         <is>
           <t>갑 (위탁자)</t>
         </is>
       </c>
-      <c r="S51" s="11" t="inlineStr">
+      <c r="Q57" s="16" t="n"/>
+      <c r="U57" s="17" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="K52" s="12" t="inlineStr">
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="14" t="inlineStr"/>
+      <c r="K58" s="15" t="inlineStr">
         <is>
           <t>을 (운반자)</t>
         </is>
       </c>
-      <c r="S52" s="11" t="inlineStr">
+      <c r="Q58" s="16" t="n"/>
+      <c r="U58" s="17" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="6" customHeight="1"/>
-    <row r="56">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="59" ht="6" customHeight="1"/>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="65">
+  <mergeCells count="70">
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="U58:X58"/>
     <mergeCell ref="G7:X7"/>
-    <mergeCell ref="V44:X44"/>
     <mergeCell ref="A16:X16"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A25:X25"/>
-    <mergeCell ref="A45:B45"/>
     <mergeCell ref="G10:X10"/>
-    <mergeCell ref="L45:N45"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="G13:X13"/>
-    <mergeCell ref="A37:X37"/>
-    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="A46:X46"/>
+    <mergeCell ref="L51:N51"/>
+    <mergeCell ref="K58:P58"/>
     <mergeCell ref="A18:X18"/>
     <mergeCell ref="A27:X27"/>
-    <mergeCell ref="A56:X56"/>
+    <mergeCell ref="V49:X49"/>
     <mergeCell ref="A3:X3"/>
     <mergeCell ref="A21:X21"/>
-    <mergeCell ref="K51:R51"/>
-    <mergeCell ref="A50:X50"/>
+    <mergeCell ref="V51:X51"/>
+    <mergeCell ref="A56:X56"/>
+    <mergeCell ref="Q57:T57"/>
+    <mergeCell ref="A58:J58"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="V45:X45"/>
+    <mergeCell ref="L50:N50"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="L44:N44"/>
+    <mergeCell ref="C50:G50"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A42:X42"/>
     <mergeCell ref="A33:X33"/>
     <mergeCell ref="G14:X14"/>
-    <mergeCell ref="A47:X47"/>
-    <mergeCell ref="O43:U43"/>
-    <mergeCell ref="H43:K43"/>
     <mergeCell ref="A22:X22"/>
-    <mergeCell ref="H44:K44"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="V50:X50"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="L49:N49"/>
+    <mergeCell ref="A53:X53"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="O45:U45"/>
-    <mergeCell ref="K52:R52"/>
+    <mergeCell ref="A43:X43"/>
+    <mergeCell ref="K57:P57"/>
+    <mergeCell ref="A62:X62"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A28:X28"/>
+    <mergeCell ref="C51:G51"/>
     <mergeCell ref="A19:X19"/>
-    <mergeCell ref="V43:X43"/>
-    <mergeCell ref="S51:X51"/>
     <mergeCell ref="G9:X9"/>
+    <mergeCell ref="O49:U49"/>
     <mergeCell ref="A31:X31"/>
-    <mergeCell ref="A40:X40"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="Q58:T58"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="G12:X12"/>
     <mergeCell ref="A30:X30"/>
     <mergeCell ref="A34:X34"/>
-    <mergeCell ref="A39:X39"/>
-    <mergeCell ref="O44:U44"/>
-    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="U57:X57"/>
     <mergeCell ref="A24:X24"/>
     <mergeCell ref="G11:X11"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="O50:U50"/>
+    <mergeCell ref="A57:J57"/>
     <mergeCell ref="M1:X1"/>
-    <mergeCell ref="L43:N43"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="A36:X36"/>
+    <mergeCell ref="A45:X45"/>
+    <mergeCell ref="A61:X61"/>
+    <mergeCell ref="O51:U51"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="G8:X8"/>
-    <mergeCell ref="S52:X52"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>운  반  계  약  서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  운반 품목</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>사토(터파기 잔토)</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  상차 장소</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>STA.0+420 현장</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  하차 장소</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>가나시 사토장(허가 제0000호)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  운반 거리</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>편도 8km</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  단가 기준</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>㎥당(덤프 15t · 6㎥ 기준)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="5" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  단    가</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>㎥당 9,800원(부가세 별도)</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="5" t="n"/>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  운반 기간</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>2026. 10. 1. ~ 2026. 10. 31.</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="5" t="n"/>
+      <c r="V12" s="5" t="n"/>
+      <c r="W12" s="5" t="n"/>
+      <c r="X12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  대기료</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>시간당 30,000원(1시간 넘는 대기부터)</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="5" t="n"/>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  대금 지급기한</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>월말 정산 후 다음 달 15일</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="5" t="n"/>
+      <c r="T14" s="5" t="n"/>
+      <c r="U14" s="5" t="n"/>
+      <c r="V14" s="5" t="n"/>
+      <c r="W14" s="5" t="n"/>
+      <c r="X14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="6" customHeight="1"/>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>위탁자(이하 「갑」)와 운반자(이하 「을」)는 위 운반에 관하여 다음과 같이 계약을 체결한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="6" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>제1조 (목적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="43.5" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>을은 갑이 지정한 품목을 상차 장소에서 하차 장소까지 운반하고, 갑은 그 대가를 지급한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="4" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>제2조 (운반 단가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="43.5" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>운반 대가는 위 단가 기준에 따라 산정한다. 기준이 바뀌는 경우 서면으로 합의한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="4" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>제3조 (적재량 준수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="43.5" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>을은 관계 법령에서 정한 적재량과 운행 기준을 지킨다. 과적으로 발생한 책임은 을이 진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="4" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>제4조 (대기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="29" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>갑의 사정으로 상·하차가 지연된 때에는 위 대기료를 지급한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="4" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>제5조 (운반물의 관리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="43.5" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>운반 중 운반물의 멸실·훼손에 대한 책임은 을이 진다. 다만 갑의 지시나 불가항력에 의한 경우는 그러하지 아니하다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="4" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>제6조 (허가와 보험)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="29" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>폐기물 등 허가가 필요한 운반은 을이 유효한 허가와 보험을 갖춘다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="4" customHeight="1"/>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="8" customHeight="1"/>
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="8" customHeight="1"/>
+    <row r="40" ht="8" customHeight="1"/>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>제7조 (대금의 지급)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="29" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>갑은 운반 완료를 확인한 후 위 지급기한 안에 대금을 지급한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="4" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>제8조 (분쟁의 해결)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="43.5" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>분쟁은 협의로 해결하되, 협의가 되지 아니한 때에는 관할 법원의 판결에 따른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="4" customHeight="1"/>
+    <row r="48" ht="6" customHeight="1"/>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>상호(성명)</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>사업자등록번호</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="10" t="inlineStr">
+        <is>
+          <t>대표자</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="n"/>
+      <c r="O49" s="10" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="P49" s="5" t="n"/>
+      <c r="Q49" s="5" t="n"/>
+      <c r="R49" s="5" t="n"/>
+      <c r="S49" s="5" t="n"/>
+      <c r="T49" s="5" t="n"/>
+      <c r="U49" s="5" t="n"/>
+      <c r="V49" s="10" t="inlineStr">
+        <is>
+          <t>연락처</t>
+        </is>
+      </c>
+      <c r="W49" s="5" t="n"/>
+      <c r="X49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>갑</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>예시건설(주)</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="n"/>
+      <c r="O50" s="12" t="inlineStr">
+        <is>
+          <t>가나시 마바로 45, 2층</t>
+        </is>
+      </c>
+      <c r="P50" s="5" t="n"/>
+      <c r="Q50" s="5" t="n"/>
+      <c r="R50" s="5" t="n"/>
+      <c r="S50" s="5" t="n"/>
+      <c r="T50" s="5" t="n"/>
+      <c r="U50" s="5" t="n"/>
+      <c r="V50" s="11" t="inlineStr">
+        <is>
+          <t>000-000-0000</t>
+        </is>
+      </c>
+      <c r="W50" s="5" t="n"/>
+      <c r="X50" s="5" t="n"/>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>을</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>예시운수</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="11" t="inlineStr">
+        <is>
+          <t>운대표</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="12" t="inlineStr">
+        <is>
+          <t>가나시 물류로 5</t>
+        </is>
+      </c>
+      <c r="P51" s="5" t="n"/>
+      <c r="Q51" s="5" t="n"/>
+      <c r="R51" s="5" t="n"/>
+      <c r="S51" s="5" t="n"/>
+      <c r="T51" s="5" t="n"/>
+      <c r="U51" s="5" t="n"/>
+      <c r="V51" s="11" t="inlineStr">
+        <is>
+          <t>000-000-0000</t>
+        </is>
+      </c>
+      <c r="W51" s="5" t="n"/>
+      <c r="X51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="6" customHeight="1"/>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="6" customHeight="1"/>
+    <row r="55" ht="10" customHeight="1"/>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="13" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="14" t="inlineStr"/>
+      <c r="K57" s="15" t="inlineStr">
+        <is>
+          <t>갑 (위탁자)</t>
+        </is>
+      </c>
+      <c r="Q57" s="16" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="U57" s="17" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="14" t="inlineStr"/>
+      <c r="K58" s="15" t="inlineStr">
+        <is>
+          <t>을 (운반자)</t>
+        </is>
+      </c>
+      <c r="Q58" s="16" t="inlineStr">
+        <is>
+          <t>운대표</t>
+        </is>
+      </c>
+      <c r="U58" s="17" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="6" customHeight="1"/>
+    <row r="61" ht="19.5" customHeight="1">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="69">
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="U58:X58"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="A16:X16"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A25:X25"/>
+    <mergeCell ref="G10:X10"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="G13:X13"/>
+    <mergeCell ref="A46:X46"/>
+    <mergeCell ref="L51:N51"/>
+    <mergeCell ref="K58:P58"/>
+    <mergeCell ref="A18:X18"/>
+    <mergeCell ref="A27:X27"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="A21:X21"/>
+    <mergeCell ref="V51:X51"/>
+    <mergeCell ref="A56:X56"/>
+    <mergeCell ref="Q57:T57"/>
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="L50:N50"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A42:X42"/>
+    <mergeCell ref="A33:X33"/>
+    <mergeCell ref="G14:X14"/>
+    <mergeCell ref="A22:X22"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="V50:X50"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="L49:N49"/>
+    <mergeCell ref="A53:X53"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A43:X43"/>
+    <mergeCell ref="K57:P57"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A28:X28"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="A19:X19"/>
+    <mergeCell ref="G9:X9"/>
+    <mergeCell ref="O49:U49"/>
+    <mergeCell ref="A31:X31"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="Q58:T58"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="G12:X12"/>
+    <mergeCell ref="A30:X30"/>
+    <mergeCell ref="A34:X34"/>
+    <mergeCell ref="U57:X57"/>
+    <mergeCell ref="A24:X24"/>
+    <mergeCell ref="G11:X11"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="O50:U50"/>
+    <mergeCell ref="A57:J57"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="A45:X45"/>
+    <mergeCell ref="A61:X61"/>
+    <mergeCell ref="O51:U51"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G8:X8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/gy-unban.xlsx
+++ b/web/public/forms/gy-unban.xlsx
@@ -586,7 +586,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1328,7 +1328,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="19" t="inlineStr">

--- a/web/public/forms/gy-unban.xlsx
+++ b/web/public/forms/gy-unban.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="운반계약서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'운반계약서'!$A$1:$X$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -132,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -185,9 +183,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1196,6 +1191,7 @@
       </c>
     </row>
     <row r="59" ht="6" customHeight="1"/>
+    <row r="60"/>
     <row r="61" ht="34" customHeight="1">
       <c r="A61" s="18" t="inlineStr">
         <is>
@@ -1287,824 +1283,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>운  반  계  약  서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  운반 품목</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>사토(터파기 잔토)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  상차 장소</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>STA.0+420 현장</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  하차 장소</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>가나시 사토장(허가 제0000호)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  운반 거리</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>편도 8km</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  단가 기준</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>㎥당(덤프 15t · 6㎥ 기준)</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="5" t="n"/>
-      <c r="V10" s="5" t="n"/>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  단    가</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>㎥당 9,800원(부가세 별도)</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="5" t="n"/>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  운반 기간</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>2026. 10. 1. ~ 2026. 10. 31.</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  대기료</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>시간당 30,000원(1시간 넘는 대기부터)</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="5" t="n"/>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="5" t="n"/>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  대금 지급기한</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>월말 정산 후 다음 달 15일</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="5" t="n"/>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="5" t="n"/>
-      <c r="V14" s="5" t="n"/>
-      <c r="W14" s="5" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="6" customHeight="1"/>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>위탁자(이하 「갑」)와 운반자(이하 「을」)는 위 운반에 관하여 다음과 같이 계약을 체결한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="6" customHeight="1"/>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>제1조 (목적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="43.5" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>을은 갑이 지정한 품목을 상차 장소에서 하차 장소까지 운반하고, 갑은 그 대가를 지급한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="4" customHeight="1"/>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>제2조 (운반 단가)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="43.5" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>운반 대가는 위 단가 기준에 따라 산정한다. 기준이 바뀌는 경우 서면으로 합의한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="4" customHeight="1"/>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>제3조 (적재량 준수)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="43.5" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>을은 관계 법령에서 정한 적재량과 운행 기준을 지킨다. 과적으로 발생한 책임은 을이 진다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="4" customHeight="1"/>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>제4조 (대기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="29" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>갑의 사정으로 상·하차가 지연된 때에는 위 대기료를 지급한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="4" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>제5조 (운반물의 관리)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="43.5" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>운반 중 운반물의 멸실·훼손에 대한 책임은 을이 진다. 다만 갑의 지시나 불가항력에 의한 경우는 그러하지 아니하다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="4" customHeight="1"/>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>제6조 (허가와 보험)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="29" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>폐기물 등 허가가 필요한 운반은 을이 유효한 허가와 보험을 갖춘다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="4" customHeight="1"/>
-    <row r="36" ht="8" customHeight="1"/>
-    <row r="37" ht="8" customHeight="1"/>
-    <row r="38" ht="8" customHeight="1"/>
-    <row r="39" ht="8" customHeight="1"/>
-    <row r="40" ht="8" customHeight="1"/>
-    <row r="41" ht="8" customHeight="1"/>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>제7조 (대금의 지급)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="29" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>갑은 운반 완료를 확인한 후 위 지급기한 안에 대금을 지급한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="4" customHeight="1"/>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>제8조 (분쟁의 해결)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="43.5" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>분쟁은 협의로 해결하되, 협의가 되지 아니한 때에는 관할 법원의 판결에 따른다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="4" customHeight="1"/>
-    <row r="48" ht="6" customHeight="1"/>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>상호(성명)</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>사업자등록번호</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="n"/>
-      <c r="L49" s="10" t="inlineStr">
-        <is>
-          <t>대표자</t>
-        </is>
-      </c>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="n"/>
-      <c r="O49" s="10" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="P49" s="5" t="n"/>
-      <c r="Q49" s="5" t="n"/>
-      <c r="R49" s="5" t="n"/>
-      <c r="S49" s="5" t="n"/>
-      <c r="T49" s="5" t="n"/>
-      <c r="U49" s="5" t="n"/>
-      <c r="V49" s="10" t="inlineStr">
-        <is>
-          <t>연락처</t>
-        </is>
-      </c>
-      <c r="W49" s="5" t="n"/>
-      <c r="X49" s="5" t="n"/>
-    </row>
-    <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>갑</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="n"/>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>000-00-00000</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
-      <c r="L50" s="11" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="n"/>
-      <c r="O50" s="12" t="inlineStr">
-        <is>
-          <t>가나시 마바로 45, 2층</t>
-        </is>
-      </c>
-      <c r="P50" s="5" t="n"/>
-      <c r="Q50" s="5" t="n"/>
-      <c r="R50" s="5" t="n"/>
-      <c r="S50" s="5" t="n"/>
-      <c r="T50" s="5" t="n"/>
-      <c r="U50" s="5" t="n"/>
-      <c r="V50" s="11" t="inlineStr">
-        <is>
-          <t>000-000-0000</t>
-        </is>
-      </c>
-      <c r="W50" s="5" t="n"/>
-      <c r="X50" s="5" t="n"/>
-    </row>
-    <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>을</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>예시운수</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="11" t="inlineStr">
-        <is>
-          <t>000-00-00000</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="n"/>
-      <c r="L51" s="11" t="inlineStr">
-        <is>
-          <t>운대표</t>
-        </is>
-      </c>
-      <c r="M51" s="5" t="n"/>
-      <c r="N51" s="5" t="n"/>
-      <c r="O51" s="12" t="inlineStr">
-        <is>
-          <t>가나시 물류로 5</t>
-        </is>
-      </c>
-      <c r="P51" s="5" t="n"/>
-      <c r="Q51" s="5" t="n"/>
-      <c r="R51" s="5" t="n"/>
-      <c r="S51" s="5" t="n"/>
-      <c r="T51" s="5" t="n"/>
-      <c r="U51" s="5" t="n"/>
-      <c r="V51" s="11" t="inlineStr">
-        <is>
-          <t>000-000-0000</t>
-        </is>
-      </c>
-      <c r="W51" s="5" t="n"/>
-      <c r="X51" s="5" t="n"/>
-    </row>
-    <row r="52" ht="6" customHeight="1"/>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="6" customHeight="1"/>
-    <row r="55" ht="10" customHeight="1"/>
-    <row r="56" ht="26" customHeight="1">
-      <c r="A56" s="13" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="14" t="inlineStr"/>
-      <c r="K57" s="15" t="inlineStr">
-        <is>
-          <t>갑 (위탁자)</t>
-        </is>
-      </c>
-      <c r="Q57" s="16" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="U57" s="17" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="14" t="inlineStr"/>
-      <c r="K58" s="15" t="inlineStr">
-        <is>
-          <t>을 (운반자)</t>
-        </is>
-      </c>
-      <c r="Q58" s="16" t="inlineStr">
-        <is>
-          <t>운대표</t>
-        </is>
-      </c>
-      <c r="U58" s="17" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="6" customHeight="1"/>
-    <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="18" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="69">
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="U58:X58"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="A16:X16"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A25:X25"/>
-    <mergeCell ref="G10:X10"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="G13:X13"/>
-    <mergeCell ref="A46:X46"/>
-    <mergeCell ref="L51:N51"/>
-    <mergeCell ref="K58:P58"/>
-    <mergeCell ref="A18:X18"/>
-    <mergeCell ref="A27:X27"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="A21:X21"/>
-    <mergeCell ref="V51:X51"/>
-    <mergeCell ref="A56:X56"/>
-    <mergeCell ref="Q57:T57"/>
-    <mergeCell ref="A58:J58"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="L50:N50"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A42:X42"/>
-    <mergeCell ref="A33:X33"/>
-    <mergeCell ref="G14:X14"/>
-    <mergeCell ref="A22:X22"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="L49:N49"/>
-    <mergeCell ref="A53:X53"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A43:X43"/>
-    <mergeCell ref="K57:P57"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A28:X28"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="A19:X19"/>
-    <mergeCell ref="G9:X9"/>
-    <mergeCell ref="O49:U49"/>
-    <mergeCell ref="A31:X31"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="H51:K51"/>
-    <mergeCell ref="Q58:T58"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="G12:X12"/>
-    <mergeCell ref="A30:X30"/>
-    <mergeCell ref="A34:X34"/>
-    <mergeCell ref="U57:X57"/>
-    <mergeCell ref="A24:X24"/>
-    <mergeCell ref="G11:X11"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="O50:U50"/>
-    <mergeCell ref="A57:J57"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="A45:X45"/>
-    <mergeCell ref="A61:X61"/>
-    <mergeCell ref="O51:U51"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G8:X8"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/gy-unban.xlsx
+++ b/web/public/forms/gy-unban.xlsx
@@ -581,7 +581,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
